--- a/RaidenDemo/文档/配置表/__enums__.xlsx
+++ b/RaidenDemo/文档/配置表/__enums__.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R438edbd39397479d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5c2de565c1e54b32"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -329,7 +329,7 @@
     <x:numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <x:numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </x:numFmts>
-  <x:fonts count="24">
+  <x:fonts count="25">
     <x:font>
       <x:sz val="11"/>
       <x:color theme="1"/>
@@ -458,6 +458,11 @@
       <x:sz val="11"/>
       <x:color rgb="FF000000"/>
       <x:name val="微软雅黑"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="等线"/>
     </x:font>
   </x:fonts>
   <x:fills count="34">
@@ -1275,7 +1280,7 @@
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="101">
+  <x:cellXfs count="114">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment vertical="center"/>
     </x:xf>
@@ -1648,6 +1653,45 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="70" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="49">
@@ -3257,27 +3301,51 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="K68" s="97"/>
-      <x:c r="L68"/>
+      <x:c r="L68" s="101"/>
     </x:row>
     <x:row r="69">
-      <x:c r="B69" s="98"/>
-      <x:c r="C69" s="99"/>
-      <x:c r="D69" s="99"/>
-      <x:c r="E69" s="99"/>
-      <x:c r="F69" s="99"/>
-      <x:c r="G69" s="99"/>
-      <x:c r="H69" s="99" t="str">
+      <x:c r="A69"/>
+      <x:c r="B69" s="102"/>
+      <x:c r="C69" s="103"/>
+      <x:c r="D69" s="103"/>
+      <x:c r="E69" s="103"/>
+      <x:c r="F69" s="103"/>
+      <x:c r="G69" s="103"/>
+      <x:c r="H69" s="103" t="str">
+        <x:v>BULLET_LAUNCH</x:v>
+      </x:c>
+      <x:c r="I69" s="103" t="str">
+        <x:v>子弹发射特效</x:v>
+      </x:c>
+      <x:c r="J69" s="103" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K69" s="104" t="str">
+        <x:v>子弹实际创建时播放的发射特效</x:v>
+      </x:c>
+      <x:c r="L69" s="105"/>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" s="111"/>
+      <x:c r="B70" s="112"/>
+      <x:c r="C70" s="111"/>
+      <x:c r="D70" s="111"/>
+      <x:c r="E70" s="111"/>
+      <x:c r="F70" s="111"/>
+      <x:c r="G70" s="111"/>
+      <x:c r="H70" s="111" t="str">
         <x:v>OTHER</x:v>
       </x:c>
-      <x:c r="I69" s="99" t="str">
+      <x:c r="I70" s="111" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="J69" s="99" t="n">
+      <x:c r="J70" s="111" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K69" s="100" t="str">
+      <x:c r="K70" s="111" t="str">
         <x:v>通用或暂未独立分类的演出特效</x:v>
       </x:c>
+      <x:c r="L70" s="113"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/RaidenDemo/文档/配置表/__enums__.xlsx
+++ b/RaidenDemo/文档/配置表/__enums__.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5c2de565c1e54b32"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc57125a49f714451"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -465,7 +465,7 @@
       <x:name val="等线"/>
     </x:font>
   </x:fonts>
-  <x:fills count="34">
+  <x:fills count="35">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -632,8 +632,13 @@
         <x:fgColor theme="9" tint="0.39998"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="71">
+  <x:borders count="81">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -1130,6 +1135,64 @@
         <x:color rgb="FF808080"/>
       </x:bottom>
     </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="none"/>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:right style="none"/>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="thin">
+        <x:color rgb="FF7F7F7F"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FF7F7F7F"/>
+      </x:top>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:top style="thin">
+        <x:color rgb="FF7F7F7F"/>
+      </x:top>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:right style="thin">
+        <x:color rgb="FF7F7F7F"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF7F7F7F"/>
+      </x:top>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="thin">
+        <x:color rgb="FF7F7F7F"/>
+      </x:left>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:right style="thin">
+        <x:color rgb="FF7F7F7F"/>
+      </x:right>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="thin">
+        <x:color rgb="FF7F7F7F"/>
+      </x:left>
+      <x:bottom style="thin">
+        <x:color rgb="FF7F7F7F"/>
+      </x:bottom>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:bottom style="thin">
+        <x:color rgb="FF7F7F7F"/>
+      </x:bottom>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:right style="thin">
+        <x:color rgb="FF7F7F7F"/>
+      </x:right>
+      <x:bottom style="thin">
+        <x:color rgb="FF7F7F7F"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="49">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1280,7 +1343,7 @@
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="114">
+  <x:cellXfs count="141">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment vertical="center"/>
     </x:xf>
@@ -1691,6 +1754,117 @@
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="34" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="34" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="34" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="34" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="34" borderId="71" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="34" borderId="72" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="34" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="34" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="34" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="34" borderId="73" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="34" borderId="74" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="34" borderId="74" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="34" borderId="75" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="34" borderId="76" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="34" borderId="77" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="34" borderId="78" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="34" borderId="79" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="34" borderId="80" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
   </x:cellXfs>
@@ -3347,6 +3521,94 @@
       </x:c>
       <x:c r="L70" s="113"/>
     </x:row>
+    <x:row r="72">
+      <x:c r="A72" s="122"/>
+      <x:c r="B72" s="132" t="str">
+        <x:v>StageItemType</x:v>
+      </x:c>
+      <x:c r="C72" s="133" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D72" s="133" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E72" s="134"/>
+      <x:c r="F72" s="134" t="str">
+        <x:v>关卡道具类型</x:v>
+      </x:c>
+      <x:c r="G72" s="134"/>
+      <x:c r="H72" s="134" t="str">
+        <x:v>PLAYER_UPGRADE</x:v>
+      </x:c>
+      <x:c r="I72" s="134" t="str">
+        <x:v>玩家升级</x:v>
+      </x:c>
+      <x:c r="J72" s="134" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K72" s="134"/>
+      <x:c r="L72" s="135"/>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" s="126"/>
+      <x:c r="B73" s="136"/>
+      <x:c r="C73" s="127"/>
+      <x:c r="D73" s="127"/>
+      <x:c r="E73" s="127"/>
+      <x:c r="F73" s="127"/>
+      <x:c r="G73" s="127"/>
+      <x:c r="H73" s="127" t="str">
+        <x:v>WINGMAN_UPGRADE</x:v>
+      </x:c>
+      <x:c r="I73" s="127" t="str">
+        <x:v>僚机升级</x:v>
+      </x:c>
+      <x:c r="J73" s="127" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K73" s="127"/>
+      <x:c r="L73" s="137"/>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" s="126"/>
+      <x:c r="B74" s="136"/>
+      <x:c r="C74" s="127"/>
+      <x:c r="D74" s="127"/>
+      <x:c r="E74" s="127"/>
+      <x:c r="F74" s="127"/>
+      <x:c r="G74" s="127"/>
+      <x:c r="H74" s="127" t="str">
+        <x:v>HEALTH</x:v>
+      </x:c>
+      <x:c r="I74" s="127" t="str">
+        <x:v>回血</x:v>
+      </x:c>
+      <x:c r="J74" s="127" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K74" s="127"/>
+      <x:c r="L74" s="137"/>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" s="129"/>
+      <x:c r="B75" s="138"/>
+      <x:c r="C75" s="139"/>
+      <x:c r="D75" s="139"/>
+      <x:c r="E75" s="139"/>
+      <x:c r="F75" s="139"/>
+      <x:c r="G75" s="139"/>
+      <x:c r="H75" s="139" t="str">
+        <x:v>LIFE</x:v>
+      </x:c>
+      <x:c r="I75" s="139" t="str">
+        <x:v>加命</x:v>
+      </x:c>
+      <x:c r="J75" s="139" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K75" s="139"/>
+      <x:c r="L75" s="140"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="H1:L1"/>
